--- a/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0003T0006Z000C1N30_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0003T0006Z000C1N30_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>32.07018156924022</v>
+        <v>5.211404505001536</v>
       </c>
       <c r="D2" t="n">
-        <v>32.01766783288737</v>
+        <v>5.202871022844198</v>
       </c>
       <c r="E2" t="n">
-        <v>9.657473565031554</v>
+        <v>1.569339454317628</v>
       </c>
       <c r="F2" t="n">
-        <v>10.49946069873064</v>
+        <v>1.70616236354373</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>33.31209650963119</v>
+        <v>5.413215682815069</v>
       </c>
       <c r="D3" t="n">
-        <v>31.1074895241758</v>
+        <v>5.054967047678568</v>
       </c>
       <c r="E3" t="n">
-        <v>9.657473565031554</v>
+        <v>1.569339454317628</v>
       </c>
       <c r="F3" t="n">
-        <v>10.49946069873064</v>
+        <v>1.70616236354373</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>49.13080450905896</v>
+        <v>7.983755732722082</v>
       </c>
       <c r="D4" t="n">
-        <v>48.93596076967857</v>
+        <v>7.952093625072768</v>
       </c>
       <c r="E4" t="n">
-        <v>9.657473565031554</v>
+        <v>1.569339454317628</v>
       </c>
       <c r="F4" t="n">
-        <v>10.49946069873064</v>
+        <v>1.70616236354373</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>20.49245652765132</v>
+        <v>3.33002418574334</v>
       </c>
       <c r="D5" t="n">
-        <v>16.81972238844892</v>
+        <v>2.73320488812295</v>
       </c>
       <c r="E5" t="n">
-        <v>9.657473565031554</v>
+        <v>1.569339454317628</v>
       </c>
       <c r="F5" t="n">
-        <v>10.49946069873064</v>
+        <v>1.70616236354373</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>25.76789945976899</v>
+        <v>4.187283662212462</v>
       </c>
       <c r="D6" t="n">
-        <v>25.76625183111112</v>
+        <v>4.187015922555557</v>
       </c>
       <c r="E6" t="n">
-        <v>9.657473565031554</v>
+        <v>1.569339454317628</v>
       </c>
       <c r="F6" t="n">
-        <v>10.49946069873064</v>
+        <v>1.70616236354373</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
